--- a/data/vessels/2026-10-20.xlsx
+++ b/data/vessels/2026-10-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="441321" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBAD723E-7E39-4460-B864-5AB600294DAA}"/>
+  <xr:revisionPtr revIDLastSave="441667" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C6E43CF-0C12-4351-8694-D4AAAEEA3AC1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="214">
   <si>
     <t>Harbor</t>
   </si>
@@ -152,6 +152,24 @@
     <t>SSA Marine</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
     <t>T5</t>
   </si>
   <si>
@@ -167,24 +185,6 @@
     <t>MSC</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -386,7 +386,19 @@
     <t>YM PLUM</t>
   </si>
   <si>
-    <t>PN12640W</t>
+    <t>PN12640E</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
   </si>
   <si>
     <t>Blair</t>
@@ -395,18 +407,6 @@
     <t>LIBERTY PASSION</t>
   </si>
   <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
     <t>FRANKFURT EXPRESS</t>
   </si>
   <si>
@@ -461,16 +461,16 @@
     <t>MC637A</t>
   </si>
   <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
-    <t>JNBB0001E</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
+    <t>PN32639E</t>
   </si>
   <si>
     <t>MORNING LUCY</t>
@@ -491,7 +491,7 @@
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
-    <t>HHFW0172E</t>
+    <t>PN32640W</t>
   </si>
   <si>
     <t>Not Specified</t>
@@ -500,6 +500,9 @@
     <t>CYPRESS</t>
   </si>
   <si>
+    <t>CPN0K0S19</t>
+  </si>
+  <si>
     <t>EUROPEAN HIGHWAY</t>
   </si>
   <si>
@@ -515,7 +518,7 @@
     <t>ONE MAJESTY</t>
   </si>
   <si>
-    <t>JMJT0026E</t>
+    <t>PN12641E</t>
   </si>
   <si>
     <t>EVER SMILE</t>
@@ -563,12 +566,12 @@
     <t>Jones Stevedoring Co</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
   </si>
   <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
     <t>MSC SABRINA</t>
   </si>
   <si>
@@ -578,7 +581,7 @@
     <t>CORNEILLE</t>
   </si>
   <si>
-    <t>JCLL0014E</t>
+    <t>PN12642W</t>
   </si>
   <si>
     <t>WESTWOOD COLUMBIA</t>
@@ -593,7 +596,7 @@
     <t>OOCL SEATTLE</t>
   </si>
   <si>
-    <t>46E</t>
+    <t>DAH0C0E19</t>
   </si>
   <si>
     <t>COSCO SANTOS</t>
@@ -611,13 +614,16 @@
     <t>LOTUS A</t>
   </si>
   <si>
+    <t>CPN080S19</t>
+  </si>
+  <si>
     <t>GLOVIS TRUST</t>
   </si>
   <si>
     <t>ONE MODERN</t>
   </si>
   <si>
-    <t>JMOD0083E</t>
+    <t>PN32641E</t>
   </si>
   <si>
     <t>TOURMALINE ACE</t>
@@ -635,7 +641,7 @@
     <t>EVER SUMMIT</t>
   </si>
   <si>
-    <t>498-133E</t>
+    <t>NWX0E0S19</t>
   </si>
   <si>
     <t>SUPREME ACE</t>
@@ -659,22 +665,22 @@
     <t>MC639A</t>
   </si>
   <si>
+    <t>YM MANDATE</t>
+  </si>
+  <si>
+    <t>PN12643W</t>
+  </si>
+  <si>
+    <t>XIN ZHAN JIANG</t>
+  </si>
+  <si>
+    <t>201N</t>
+  </si>
+  <si>
     <t>OOCL OAKLAND</t>
   </si>
   <si>
-    <t>145E</t>
-  </si>
-  <si>
-    <t>YM MANDATE</t>
-  </si>
-  <si>
-    <t>JMDT0606E</t>
-  </si>
-  <si>
-    <t>XIN ZHAN JIANG</t>
-  </si>
-  <si>
-    <t>201N</t>
+    <t>DAH0E0E19</t>
   </si>
 </sst>
 </file>
@@ -747,10 +753,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L108" totalsRowShown="0">
-  <autoFilter ref="A1:L108" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L108">
-    <sortCondition ref="J2:J108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L109" totalsRowShown="0">
+  <autoFilter ref="A1:L109" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L109">
+    <sortCondition ref="J2:J109"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1087,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1281,7 +1287,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
@@ -1299,7 +1305,7 @@
         <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -1316,25 +1322,25 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
@@ -1439,7 +1445,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
         <v>23</v>
@@ -1795,7 +1801,7 @@
         <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
         <v>36</v>
@@ -2008,7 +2014,7 @@
         <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
@@ -2101,7 +2107,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
         <v>98</v>
@@ -2113,10 +2119,10 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
@@ -2235,10 +2241,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
         <v>112</v>
@@ -2247,7 +2253,7 @@
         <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I33" t="s">
         <v>18</v>
@@ -2267,10 +2273,10 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
         <v>114</v>
@@ -2279,10 +2285,10 @@
         <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
@@ -2302,19 +2308,22 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>117</v>
       </c>
       <c r="F35" t="s">
         <v>118</v>
       </c>
       <c r="G35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
         <v>119</v>
@@ -2326,7 +2335,7 @@
         <v>46322.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L35" t="s">
         <v>19</v>
@@ -2337,22 +2346,19 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" s="1" t="s">
         <v>121</v>
       </c>
       <c r="F36" t="s">
         <v>118</v>
       </c>
       <c r="G36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
         <v>119</v>
@@ -2364,7 +2370,7 @@
         <v>46322.25</v>
       </c>
       <c r="K36" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L36" t="s">
         <v>19</v>
@@ -2512,7 +2518,7 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -2576,7 +2582,7 @@
         <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
         <v>129</v>
@@ -2588,7 +2594,7 @@
         <v>131</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
@@ -2701,7 +2707,7 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
         <v>129</v>
@@ -2713,7 +2719,7 @@
         <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
@@ -2768,13 +2774,13 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
         <v>140</v>
@@ -2783,7 +2789,7 @@
         <v>141</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
@@ -2792,7 +2798,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K49" s="2">
-        <v>46328.916666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L49" t="s">
         <v>30</v>
@@ -2800,13 +2806,13 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="D50" t="s">
         <v>142</v>
@@ -2815,7 +2821,7 @@
         <v>143</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
@@ -2824,7 +2830,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L50" t="s">
         <v>30</v>
@@ -2870,7 +2876,7 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -2934,7 +2940,7 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -2969,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
         <v>98</v>
@@ -3009,8 +3015,8 @@
       <c r="D56" t="s">
         <v>152</v>
       </c>
-      <c r="E56" s="1">
-        <v>70</v>
+      <c r="E56" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F56" t="s">
         <v>106</v>
@@ -3033,16 +3039,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -3074,7 +3080,7 @@
         <v>93</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
@@ -3106,7 +3112,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F59" t="s">
         <v>35</v>
@@ -3129,16 +3135,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -3167,10 +3173,10 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -3199,10 +3205,10 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -3234,10 +3240,10 @@
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F63" t="s">
         <v>151</v>
@@ -3260,16 +3266,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -3301,10 +3307,10 @@
         <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
@@ -3333,10 +3339,10 @@
         <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
@@ -3394,10 +3400,10 @@
         <v>48</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F68" t="s">
         <v>151</v>
@@ -3426,10 +3432,10 @@
         <v>48</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F69" t="s">
         <v>151</v>
@@ -3481,19 +3487,19 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I71" t="s">
         <v>18</v>
@@ -3519,10 +3525,10 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F72" t="s">
         <v>56</v>
@@ -3531,7 +3537,7 @@
         <v>17</v>
       </c>
       <c r="H72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I72" t="s">
         <v>23</v>
@@ -3551,16 +3557,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E73" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
         <v>22</v>
@@ -3586,16 +3592,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E74" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F74" t="s">
         <v>22</v>
@@ -3621,19 +3627,19 @@
         <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C75" t="s">
         <v>129</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F75" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
@@ -3653,16 +3659,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C76" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F76" t="s">
         <v>151</v>
@@ -3685,16 +3691,16 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F77" t="s">
         <v>151</v>
@@ -3717,26 +3723,23 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="E78" s="1">
+        <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G78" t="s">
         <v>17</v>
       </c>
-      <c r="H78" t="s">
-        <v>173</v>
-      </c>
       <c r="I78" t="s">
         <v>23</v>
       </c>
@@ -3755,23 +3758,26 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
-      </c>
-      <c r="E79" s="1">
-        <v>10</v>
+        <v>172</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F79" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G79" t="s">
         <v>17</v>
       </c>
+      <c r="H79" t="s">
+        <v>174</v>
+      </c>
       <c r="I79" t="s">
         <v>23</v>
       </c>
@@ -3796,7 +3802,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -3831,10 +3837,10 @@
         <v>75</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F81" t="s">
         <v>78</v>
@@ -3889,7 +3895,7 @@
         <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F83" t="s">
         <v>35</v>
@@ -3915,7 +3921,7 @@
         <v>32</v>
       </c>
       <c r="D84" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F84" t="s">
         <v>35</v>
@@ -3973,10 +3979,10 @@
         <v>80</v>
       </c>
       <c r="D86" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
         <v>83</v>
@@ -4005,10 +4011,10 @@
         <v>107</v>
       </c>
       <c r="D87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F87" t="s">
         <v>110</v>
@@ -4023,7 +4029,7 @@
         <v>46334</v>
       </c>
       <c r="L87" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4034,10 +4040,10 @@
         <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -4095,10 +4101,10 @@
         <v>103</v>
       </c>
       <c r="D90" t="s">
-        <v>189</v>
-      </c>
-      <c r="E90" s="1">
-        <v>93</v>
+        <v>190</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="F90" t="s">
         <v>106</v>
@@ -4127,7 +4133,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1">
         <v>11</v>
@@ -4156,16 +4162,16 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
         <v>98</v>
       </c>
       <c r="D92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
@@ -4188,16 +4194,16 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -4229,10 +4235,10 @@
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
@@ -4264,10 +4270,10 @@
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -4296,10 +4302,10 @@
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -4322,16 +4328,16 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
@@ -4386,19 +4392,19 @@
         <v>31</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C99" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F99" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
@@ -4453,7 +4459,7 @@
         <v>135</v>
       </c>
       <c r="D101" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F101" t="s">
         <v>78</v>
@@ -4476,19 +4482,19 @@
         <v>31</v>
       </c>
       <c r="B102" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C102" t="s">
         <v>129</v>
       </c>
       <c r="D102" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F102" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
@@ -4505,31 +4511,31 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="D103" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F103" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46338.791666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K103" s="2">
-        <v>46340.166666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L103" t="s">
         <v>30</v>
@@ -4540,10 +4546,10 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C104" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D104" t="s">
         <v>208</v>
@@ -4552,7 +4558,7 @@
         <v>209</v>
       </c>
       <c r="F104" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -4569,31 +4575,31 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F105" t="s">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K105" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L105" t="s">
         <v>30</v>
@@ -4607,25 +4613,25 @@
         <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D106" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F106" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L106" t="s">
         <v>30</v>
@@ -4633,28 +4639,31 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>212</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="F107" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46339.541666666664</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K107" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L107" t="s">
         <v>30</v>
@@ -4665,27 +4674,56 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
+        <v>63</v>
+      </c>
+      <c r="C108" t="s">
+        <v>89</v>
+      </c>
+      <c r="D108" t="s">
+        <v>90</v>
+      </c>
+      <c r="F108" t="s">
+        <v>66</v>
+      </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="2">
+        <v>46339.541666666664</v>
+      </c>
+      <c r="K108" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L108" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
         <v>58</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C109" t="s">
         <v>59</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D109" t="s">
         <v>91</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F109" t="s">
         <v>62</v>
       </c>
-      <c r="I108" t="s">
-        <v>18</v>
-      </c>
-      <c r="J108" s="2">
+      <c r="I109" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="2">
         <v>46339.704861111109</v>
       </c>
-      <c r="K108" s="2">
+      <c r="K109" s="2">
         <v>46340.204861111109</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L109" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4698,12 +4736,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4841,7 +4887,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4850,26 +4896,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-20.xlsx
+++ b/data/vessels/2026-10-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="441667" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C6E43CF-0C12-4351-8694-D4AAAEEA3AC1}"/>
+  <xr:revisionPtr revIDLastSave="441899" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3FA3DE-6411-4CE1-8C5F-44E6432435A6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="215">
   <si>
     <t>Harbor</t>
   </si>
@@ -185,6 +185,9 @@
     <t>MSC</t>
   </si>
   <si>
+    <t>Waiting 0.3 days</t>
+  </si>
+  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -197,24 +200,24 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
     <t>T7</t>
   </si>
   <si>
     <t>THEMIS LEADER</t>
   </si>
   <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -461,18 +464,18 @@
     <t>MC637A</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
@@ -557,6 +560,9 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -564,9 +570,6 @@
   </si>
   <si>
     <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>GLOVIS LEGEND</t>
@@ -1352,7 +1355,7 @@
         <v>46317.75</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1363,16 +1366,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1387,7 +1390,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1398,16 +1401,16 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1422,7 +1425,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1430,7 +1433,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -1438,14 +1441,17 @@
       <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="1">
-        <v>63</v>
+      <c r="E10" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
       </c>
       <c r="I10" t="s">
         <v>23</v>
@@ -1465,25 +1471,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="E11" s="1">
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
         <v>23</v>
@@ -1503,22 +1506,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
         <v>36</v>
@@ -1541,28 +1544,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1">
         <v>26169</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" s="2">
         <v>46316.625</v>
@@ -1579,25 +1582,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
@@ -1620,16 +1623,16 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
@@ -1649,19 +1652,19 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
@@ -1684,19 +1687,19 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -1722,16 +1725,16 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
@@ -1751,19 +1754,19 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
@@ -1789,16 +1792,16 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
         <v>42</v>
@@ -1824,22 +1827,22 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H21" t="s">
         <v>36</v>
@@ -1868,10 +1871,10 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -1897,28 +1900,28 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="1">
         <v>26168</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J23" s="2">
         <v>46318.625</v>
@@ -1935,19 +1938,19 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
@@ -1973,7 +1976,7 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -2005,10 +2008,10 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26" s="1">
         <v>21</v>
@@ -2043,13 +2046,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
         <v>17</v>
@@ -2075,7 +2078,7 @@
         <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>34</v>
@@ -2110,13 +2113,13 @@
         <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F29" t="s">
         <v>41</v>
@@ -2148,10 +2151,10 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -2177,16 +2180,16 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
@@ -2209,19 +2212,19 @@
         <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
@@ -2247,10 +2250,10 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
         <v>47</v>
@@ -2279,10 +2282,10 @@
         <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
@@ -2308,25 +2311,25 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G35" t="s">
         <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
         <v>23</v>
@@ -2346,22 +2349,22 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G36" t="s">
         <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I36" t="s">
         <v>23</v>
@@ -2384,16 +2387,16 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
@@ -2422,10 +2425,10 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -2451,16 +2454,16 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
@@ -2480,28 +2483,28 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" s="1">
         <v>26173</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J40" s="2">
         <v>46323.625</v>
@@ -2518,16 +2521,16 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -2556,10 +2559,10 @@
         <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -2585,13 +2588,13 @@
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F43" t="s">
         <v>47</v>
@@ -2617,16 +2620,16 @@
         <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
@@ -2649,16 +2652,16 @@
         <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s">
         <v>18</v>
@@ -2678,16 +2681,16 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
@@ -2710,13 +2713,13 @@
         <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F47" t="s">
         <v>47</v>
@@ -2739,28 +2742,28 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E48" s="1">
         <v>26172</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J48" s="2">
         <v>46325.625</v>
@@ -2774,22 +2777,22 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
@@ -2798,7 +2801,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K49" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L49" t="s">
         <v>30</v>
@@ -2806,22 +2809,22 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
@@ -2830,7 +2833,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46328.916666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L50" t="s">
         <v>30</v>
@@ -2847,13 +2850,13 @@
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
@@ -2876,16 +2879,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -2911,16 +2914,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
         <v>18</v>
@@ -2940,19 +2943,19 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
@@ -2978,16 +2981,16 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
@@ -3010,16 +3013,16 @@
         <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
@@ -3039,16 +3042,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -3077,10 +3080,10 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
@@ -3112,7 +3115,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" t="s">
         <v>35</v>
@@ -3141,10 +3144,10 @@
         <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -3173,10 +3176,10 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -3205,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
@@ -3237,16 +3240,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
@@ -3266,16 +3269,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
@@ -3304,13 +3307,13 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
@@ -3336,13 +3339,13 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
@@ -3365,19 +3368,19 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F67" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J67" s="2">
         <v>46330.625</v>
@@ -3397,16 +3400,16 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
@@ -3429,16 +3432,16 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F69" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
@@ -3458,16 +3461,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
         <v>18</v>
@@ -3493,10 +3496,10 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F71" t="s">
         <v>47</v>
@@ -3525,20 +3528,17 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
-      </c>
-      <c r="E72" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="E72" s="1">
+        <v>10</v>
+      </c>
       <c r="F72" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G72" t="s">
         <v>17</v>
       </c>
-      <c r="H72" t="s">
-        <v>174</v>
-      </c>
       <c r="I72" t="s">
         <v>23</v>
       </c>
@@ -3563,17 +3563,20 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
+        <v>174</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E73" s="1">
-        <v>10</v>
-      </c>
       <c r="F73" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G73" t="s">
         <v>17</v>
       </c>
+      <c r="H73" t="s">
+        <v>176</v>
+      </c>
       <c r="I73" t="s">
         <v>23</v>
       </c>
@@ -3592,13 +3595,13 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -3630,13 +3633,13 @@
         <v>43</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F75" t="s">
         <v>47</v>
@@ -3665,13 +3668,13 @@
         <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I76" t="s">
         <v>18</v>
@@ -3697,13 +3700,13 @@
         <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I77" t="s">
         <v>18</v>
@@ -3723,13 +3726,13 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E78" s="1">
         <v>10</v>
@@ -3758,25 +3761,25 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F79" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G79" t="s">
         <v>17</v>
       </c>
       <c r="H79" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I79" t="s">
         <v>23</v>
@@ -3802,7 +3805,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -3834,16 +3837,16 @@
         <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
@@ -3863,16 +3866,16 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F82" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
         <v>18</v>
@@ -3895,7 +3898,7 @@
         <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
         <v>35</v>
@@ -3921,7 +3924,7 @@
         <v>32</v>
       </c>
       <c r="D84" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
         <v>35</v>
@@ -3944,16 +3947,16 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I85" t="s">
         <v>18</v>
@@ -3976,16 +3979,16 @@
         <v>32</v>
       </c>
       <c r="C86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D86" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I86" t="s">
         <v>18</v>
@@ -4008,16 +4011,16 @@
         <v>32</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F87" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I87" t="s">
         <v>18</v>
@@ -4029,7 +4032,7 @@
         <v>46334</v>
       </c>
       <c r="L87" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4040,10 +4043,10 @@
         <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -4066,16 +4069,16 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D89" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
         <v>18</v>
@@ -4098,16 +4101,16 @@
         <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
@@ -4133,7 +4136,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1">
         <v>11</v>
@@ -4165,13 +4168,13 @@
         <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D92" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
         <v>16</v>
@@ -4194,16 +4197,16 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -4235,10 +4238,10 @@
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s">
         <v>16</v>
@@ -4270,10 +4273,10 @@
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -4302,10 +4305,10 @@
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -4328,16 +4331,16 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
@@ -4360,19 +4363,22 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B98" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C98" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>204</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
@@ -4381,7 +4387,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L98" t="s">
         <v>30</v>
@@ -4389,22 +4395,19 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D99" t="s">
-        <v>203</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="F99" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
@@ -4413,7 +4416,7 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K99" s="2">
-        <v>46339.333333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L99" t="s">
         <v>30</v>
@@ -4424,19 +4427,19 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C100" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F100" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J100" s="2">
         <v>46337.625</v>
@@ -4456,13 +4459,13 @@
         <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F101" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
@@ -4485,13 +4488,13 @@
         <v>43</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D102" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F102" t="s">
         <v>47</v>
@@ -4520,10 +4523,10 @@
         <v>38</v>
       </c>
       <c r="D103" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F103" t="s">
         <v>41</v>
@@ -4552,10 +4555,10 @@
         <v>38</v>
       </c>
       <c r="D104" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F104" t="s">
         <v>41</v>
@@ -4581,16 +4584,16 @@
         <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
@@ -4613,16 +4616,16 @@
         <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
@@ -4645,16 +4648,16 @@
         <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F107" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
@@ -4674,16 +4677,16 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C108" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D108" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F108" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
@@ -4703,16 +4706,16 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F109" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
         <v>18</v>
@@ -4736,6 +4739,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4743,13 +4755,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4887,27 +4899,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-20.xlsx
+++ b/data/vessels/2026-10-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="441899" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3FA3DE-6411-4CE1-8C5F-44E6432435A6}"/>
+  <xr:revisionPtr revIDLastSave="442361" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FA09E69-3F4E-4AB7-86DE-1DF7D0D9CCC6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="213">
   <si>
     <t>Harbor</t>
   </si>
@@ -101,228 +101,228 @@
     <t>Not available</t>
   </si>
   <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>Waiting 0.3 days</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
     <t>EB1</t>
   </si>
   <si>
-    <t>MODERN LINK</t>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E/160W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
   </si>
   <si>
     <t>Hyundai Glovis</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Waiting 0.3 days</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
     <t>FP2</t>
   </si>
   <si>
@@ -335,49 +335,88 @@
     <t>ED616</t>
   </si>
   <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>PN32637W</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>PN12640E</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
     <t>SM PORTLAND</t>
   </si>
   <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
   </si>
   <si>
     <t>MSC IVANA</t>
@@ -386,148 +425,196 @@
     <t>UK642R</t>
   </si>
   <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>PN12640E</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
     <t>EVER MODE</t>
   </si>
   <si>
     <t>1473-010E</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>015E/016W</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640W</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
     <t>CLX</t>
   </si>
   <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>PN12641E</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>495-136E</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>642E</t>
+  </si>
+  <si>
     <t>MSC FLORA</t>
   </si>
   <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>638N</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640W</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN0K0S19</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>PN12641E</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>495-136E</t>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
+    <t>FP22633C</t>
+  </si>
+  <si>
+    <t>BUDAPEST EXPRESS</t>
+  </si>
+  <si>
+    <t>641E</t>
+  </si>
+  <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK640A</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC638A</t>
+  </si>
+  <si>
+    <t>CORNEILLE</t>
+  </si>
+  <si>
+    <t>PN12642W</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
+    <t>SM MUMBAI</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>DAH0C0E19</t>
+  </si>
+  <si>
+    <t>COSCO SANTOS</t>
+  </si>
+  <si>
+    <t>102N</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>1474-011E</t>
+  </si>
+  <si>
+    <t>LOTUS A</t>
+  </si>
+  <si>
+    <t>CPN080S19</t>
+  </si>
+  <si>
+    <t>GLOVIS TRUST</t>
   </si>
   <si>
     <t>SWIFT ACE</t>
@@ -536,105 +623,12 @@
     <t>152A</t>
   </si>
   <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>642E</t>
-  </si>
-  <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
-    <t>FP22633C</t>
-  </si>
-  <si>
-    <t>BUDAPEST EXPRESS</t>
-  </si>
-  <si>
-    <t>641E</t>
-  </si>
-  <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK640A</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC638A</t>
-  </si>
-  <si>
-    <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>PN12642W</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>SM MUMBAI</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>DAH0C0E19</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>102N</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>1474-011E</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>CPN080S19</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
-  </si>
-  <si>
     <t>ONE MODERN</t>
   </si>
   <si>
     <t>PN32641E</t>
   </si>
   <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
-  </si>
-  <si>
     <t>EVER STRONG</t>
   </si>
   <si>
@@ -647,16 +641,16 @@
     <t>NWX0E0S19</t>
   </si>
   <si>
+    <t>MSC LISBON IX</t>
+  </si>
+  <si>
+    <t>UK642A</t>
+  </si>
+  <si>
     <t>SUPREME ACE</t>
   </si>
   <si>
     <t>105A</t>
-  </si>
-  <si>
-    <t>MSC LISBON IX</t>
-  </si>
-  <si>
-    <t>UK642A</t>
   </si>
   <si>
     <t>LAUTOKA CHIEF</t>
@@ -756,10 +750,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L109" totalsRowShown="0">
-  <autoFilter ref="A1:L109" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L109">
-    <sortCondition ref="J2:J109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L106" totalsRowShown="0">
+  <autoFilter ref="A1:L106" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L106">
+    <sortCondition ref="J2:J106"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1096,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1191,124 +1185,124 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2">
-        <v>46314.875</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K3" s="2">
-        <v>46315.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.583333333336</v>
       </c>
       <c r="K4" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.166666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="2">
-        <v>46315.583333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46316.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -1317,30 +1311,30 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K6" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -1349,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="J7" s="2">
-        <v>46315.666666666664</v>
+        <v>46315.916666666664</v>
       </c>
       <c r="K7" s="2">
-        <v>46317.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1366,16 +1360,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1390,7 +1384,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1398,34 +1392,37 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46315.916666666664</v>
+        <v>46316.125</v>
       </c>
       <c r="K9" s="2">
-        <v>46322.166666666664</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1433,28 +1430,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J10" s="2">
         <v>46316.25</v>
@@ -1471,13 +1468,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1">
         <v>63</v>
@@ -1486,10 +1483,10 @@
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J11" s="2">
         <v>46316.25</v>
@@ -1506,37 +1503,37 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="E12" s="1">
+        <v>26169</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J12" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1544,37 +1541,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="1">
-        <v>26169</v>
+        <v>55</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J13" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46317.041666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1582,37 +1579,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2">
         <v>46317.208333333336</v>
       </c>
       <c r="K14" s="2">
-        <v>46317.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1620,31 +1611,34 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J15" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K15" s="2">
-        <v>46318.708333333336</v>
+        <v>46321.75</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1652,25 +1646,25 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J16" s="2">
         <v>46317.875</v>
@@ -1687,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1695,23 +1689,23 @@
       <c r="D17" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46317.875</v>
+        <v>46318.125</v>
       </c>
       <c r="K17" s="2">
-        <v>46321.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L17" t="s">
         <v>19</v>
@@ -1719,34 +1713,40 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>79</v>
-      </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
       <c r="J18" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1754,45 +1754,48 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
       </c>
+      <c r="E19" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
         <v>82</v>
@@ -1801,25 +1804,22 @@
         <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.25</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1827,37 +1827,37 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>87</v>
+      <c r="E21" s="1">
+        <v>26168</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J21" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1865,72 +1865,69 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" t="s">
         <v>90</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="1">
-        <v>26168</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>68</v>
-      </c>
       <c r="H23" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46318.625</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46319.041666666664</v>
+        <v>46320.083333333336</v>
       </c>
       <c r="L23" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1938,31 +1935,34 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>87</v>
+      <c r="E24" s="1">
+        <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>93</v>
+      </c>
+      <c r="G24" t="s">
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J24" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1970,34 +1970,34 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J25" s="2">
         <v>46319.208333333336</v>
       </c>
       <c r="K25" s="2">
-        <v>46319.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2005,34 +2005,34 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="1">
-        <v>21</v>
+        <v>96</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J26" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K26" s="2">
-        <v>46325.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L26" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2040,235 +2040,244 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46319.625</v>
+        <v>46320</v>
       </c>
       <c r="K28" s="2">
-        <v>46320.166666666664</v>
+        <v>46322</v>
       </c>
       <c r="L28" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46319.666666666664</v>
+        <v>46320.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46321.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>110</v>
+      </c>
+      <c r="G30" t="s">
+        <v>111</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="2">
-        <v>46320</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46322</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>37</v>
+      </c>
+      <c r="G31" t="s">
+        <v>38</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="2">
-        <v>46320.21875</v>
+        <v>46321.25</v>
       </c>
       <c r="K31" s="2">
-        <v>46324.59375</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>38</v>
+      </c>
+      <c r="H32" t="s">
+        <v>117</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J32" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K32" s="2">
-        <v>46322.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L32" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" t="s">
+        <v>117</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J33" s="2">
-        <v>46321.21875</v>
+        <v>46322.25</v>
       </c>
       <c r="K33" s="2">
-        <v>46323.21875</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2276,72 +2285,69 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46321.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L34" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J35" s="2">
-        <v>46322.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K35" s="2">
         <v>46323.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2349,34 +2355,34 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H36" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46322.25</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46322.75</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2384,69 +2390,72 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J37" s="2">
-        <v>46322.625</v>
+        <v>46323.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46325.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L37" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
       </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46323.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K38" s="2">
-        <v>46323.75</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2454,28 +2463,37 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>64</v>
+      </c>
+      <c r="E39" s="1">
+        <v>26173</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="G39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" t="s">
+        <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J39" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K39" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2483,37 +2501,34 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="1">
-        <v>26173</v>
+        <v>124</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J40" s="2">
-        <v>46323.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K40" s="2">
-        <v>46324.041666666664</v>
+        <v>46324.75</v>
       </c>
       <c r="L40" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2521,34 +2536,28 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46323.791666666664</v>
+        <v>46324</v>
       </c>
       <c r="K41" s="2">
-        <v>46324.75</v>
+        <v>46326</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2556,185 +2565,209 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="G42" t="s">
+        <v>17</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46324</v>
+        <v>46324.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46326</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>106</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>32</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46324.615277777775</v>
+        <v>46324.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46325.490277777775</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K44" s="2">
-        <v>46326.147916666669</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L44" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>138</v>
+        <v>85</v>
+      </c>
+      <c r="E45" s="1">
+        <v>26172</v>
       </c>
       <c r="F45" t="s">
-        <v>79</v>
+        <v>65</v>
+      </c>
+      <c r="G45" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" t="s">
+        <v>66</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J45" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46326.098611111112</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>136</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>63</v>
+        <v>90</v>
+      </c>
+      <c r="G46" t="s">
+        <v>91</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K46" s="2">
-        <v>46325.833333333336</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="G47" t="s">
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J47" s="2">
-        <v>46325.534722222219</v>
+        <v>46326.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46326.409722222219</v>
+        <v>46326.75</v>
       </c>
       <c r="L47" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2742,37 +2775,34 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="1">
-        <v>26172</v>
+        <v>140</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>68</v>
-      </c>
-      <c r="H48" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J48" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L48" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2780,42 +2810,39 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K49" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L49" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
         <v>143</v>
@@ -2824,19 +2851,22 @@
         <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>106</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46328.125</v>
+        <v>46328.75</v>
       </c>
       <c r="L50" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2844,31 +2874,31 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J51" s="2">
-        <v>46326.25</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K51" s="2">
-        <v>46326.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L51" t="s">
         <v>19</v>
@@ -2879,34 +2909,31 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D52" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" t="s">
-        <v>17</v>
-      </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K52" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L52" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2914,63 +2941,69 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s">
+        <v>148</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
         <v>59</v>
       </c>
-      <c r="C53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" t="s">
-        <v>149</v>
-      </c>
-      <c r="F53" t="s">
-        <v>63</v>
-      </c>
-      <c r="I53" t="s">
-        <v>18</v>
-      </c>
       <c r="J53" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46326.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L53" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46326.791666666664</v>
+        <v>46327.291666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46327.75</v>
+        <v>46329.166666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2978,98 +3011,95 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>152</v>
+        <v>16</v>
+      </c>
+      <c r="G55" t="s">
+        <v>17</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.625</v>
       </c>
       <c r="K55" s="2">
-        <v>46329.583333333336</v>
+        <v>46331.75</v>
       </c>
       <c r="L55" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F56" t="s">
-        <v>107</v>
+        <v>43</v>
+      </c>
+      <c r="G56" t="s">
+        <v>17</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K56" s="2">
-        <v>46328.541666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L56" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K57" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L57" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3077,60 +3107,63 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
         <v>157</v>
       </c>
-      <c r="E58" s="1">
-        <v>2</v>
+      <c r="E58" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
-      <c r="G58" t="s">
-        <v>17</v>
-      </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46327.625</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K58" s="2">
-        <v>46331.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L58" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I59" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46327.708333333336</v>
+        <v>46329</v>
       </c>
       <c r="K59" s="2">
-        <v>46328.833333333336</v>
+        <v>46330</v>
       </c>
       <c r="L59" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3138,63 +3171,66 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="I60" t="s">
         <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K60" s="2">
-        <v>46331.196527777778</v>
+        <v>46332.625</v>
       </c>
       <c r="L60" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="G61" t="s">
+        <v>17</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46329</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="K61" s="2">
-        <v>46330</v>
+        <v>46330.75</v>
       </c>
       <c r="L61" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3202,34 +3238,31 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D62" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
-      <c r="G62" t="s">
-        <v>17</v>
-      </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46329.25</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K62" s="2">
-        <v>46329.75</v>
+        <v>46334</v>
       </c>
       <c r="L62" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3240,7 +3273,7 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
         <v>165</v>
@@ -3249,19 +3282,19 @@
         <v>166</v>
       </c>
       <c r="F63" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K63" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L63" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3269,34 +3302,28 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>163</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="J64" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46330.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L64" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3307,7 +3334,7 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
         <v>167</v>
@@ -3316,19 +3343,19 @@
         <v>168</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K65" s="2">
-        <v>46334</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L65" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3339,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="D66" t="s">
         <v>167</v>
@@ -3348,19 +3375,19 @@
         <v>168</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K66" s="2">
-        <v>46334</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L66" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3368,39 +3395,39 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F67" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I67" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46330.625</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K67" s="2">
-        <v>46331.125</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L67" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D68" t="s">
         <v>169</v>
@@ -3409,19 +3436,19 @@
         <v>170</v>
       </c>
       <c r="F68" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.75</v>
       </c>
       <c r="K68" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.75</v>
       </c>
       <c r="L68" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3429,31 +3456,34 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>169</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="E69" s="1">
+        <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>152</v>
+        <v>93</v>
+      </c>
+      <c r="G69" t="s">
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J69" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L69" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3461,95 +3491,104 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
+        <v>172</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F70" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" t="s">
         <v>59</v>
       </c>
-      <c r="C70" t="s">
-        <v>60</v>
-      </c>
-      <c r="D70" t="s">
-        <v>92</v>
-      </c>
-      <c r="F70" t="s">
-        <v>63</v>
-      </c>
-      <c r="I70" t="s">
-        <v>18</v>
-      </c>
       <c r="J70" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K70" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.75</v>
       </c>
       <c r="L70" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>47</v>
+        <v>93</v>
+      </c>
+      <c r="G71" t="s">
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J71" s="2">
-        <v>46330.75</v>
+        <v>46331.25</v>
       </c>
       <c r="K71" s="2">
-        <v>46332.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L71" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" s="1">
-        <v>10</v>
+        <v>176</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="F72" t="s">
-        <v>22</v>
-      </c>
-      <c r="G72" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3557,37 +3596,31 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
-      </c>
-      <c r="H73" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K73" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L73" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3595,66 +3628,69 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
+        <v>178</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K74" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L74" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="G75" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" t="s">
+        <v>174</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J75" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L75" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3662,31 +3698,34 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
+      </c>
+      <c r="E76" s="1">
+        <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>152</v>
+        <v>93</v>
+      </c>
+      <c r="G76" t="s">
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J76" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K76" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L76" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3694,66 +3733,66 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>152</v>
+        <v>93</v>
+      </c>
+      <c r="G77" t="s">
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J77" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L77" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
-      </c>
-      <c r="E78" s="1">
-        <v>10</v>
+        <v>180</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="F78" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K78" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3761,104 +3800,80 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="F79" t="s">
-        <v>55</v>
-      </c>
-      <c r="G79" t="s">
-        <v>17</v>
-      </c>
-      <c r="H79" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L79" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="F80" t="s">
-        <v>22</v>
-      </c>
-      <c r="G80" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K80" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L80" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D81" t="s">
         <v>182</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="F81" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.375</v>
       </c>
       <c r="K81" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.5</v>
       </c>
       <c r="L81" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3866,80 +3881,92 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I82" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L82" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>75</v>
       </c>
       <c r="D83" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46332.375</v>
+        <v>46332.875</v>
       </c>
       <c r="K83" s="2">
-        <v>46333.5</v>
+        <v>46334.25</v>
       </c>
       <c r="L83" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>107</v>
       </c>
       <c r="D84" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F84" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
       </c>
       <c r="J84" s="2">
-        <v>46332.375</v>
+        <v>46333</v>
       </c>
       <c r="K84" s="2">
-        <v>46333.5</v>
+        <v>46334</v>
       </c>
       <c r="L84" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3947,92 +3974,89 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
-      </c>
-      <c r="C85" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>187</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F85" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="I85" t="s">
         <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46332.541666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K85" s="2">
-        <v>46333.041666666664</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L85" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C86" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D86" t="s">
-        <v>185</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="F86" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="I86" t="s">
         <v>18</v>
       </c>
       <c r="J86" s="2">
-        <v>46332.875</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K86" s="2">
-        <v>46334.25</v>
+        <v>46333.75</v>
       </c>
       <c r="L86" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D87" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I87" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46333</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L87" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4040,28 +4064,34 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>54</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="E88" s="1">
+        <v>11</v>
       </c>
       <c r="F88" t="s">
-        <v>28</v>
+        <v>93</v>
+      </c>
+      <c r="G88" t="s">
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J88" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L88" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4069,60 +4099,69 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
+        <v>54</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F89" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" t="s">
         <v>59</v>
       </c>
-      <c r="C89" t="s">
-        <v>85</v>
-      </c>
-      <c r="D89" t="s">
-        <v>86</v>
-      </c>
-      <c r="F89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I89" t="s">
-        <v>18</v>
-      </c>
       <c r="J89" s="2">
-        <v>46333.416666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46333.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L89" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F90" t="s">
-        <v>107</v>
+        <v>16</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J90" s="2">
-        <v>46333.666666666664</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46335.041666666664</v>
+        <v>46335.75</v>
       </c>
       <c r="L90" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4130,34 +4169,31 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D91" t="s">
-        <v>193</v>
-      </c>
-      <c r="E91" s="1">
-        <v>11</v>
+        <v>194</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F91" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I91" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46334.25</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46334.75</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4165,31 +4201,31 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C92" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46334.958333333336</v>
+        <v>46337</v>
       </c>
       <c r="K92" s="2">
-        <v>46337.708333333336</v>
+        <v>46339</v>
       </c>
       <c r="L92" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4197,34 +4233,31 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D93" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F93" t="s">
-        <v>16</v>
-      </c>
-      <c r="G93" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I93" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46335.25</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K93" s="2">
-        <v>46335.75</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L93" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4232,66 +4265,60 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="F94" t="s">
-        <v>16</v>
-      </c>
-      <c r="G94" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I94" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46335.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K94" s="2">
-        <v>46336.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D95" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F95" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46337</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46339</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4299,31 +4326,28 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D96" t="s">
-        <v>200</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="F96" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J96" s="2">
-        <v>46337.208333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K96" s="2">
-        <v>46340.208333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L96" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4331,7 +4355,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -4349,13 +4373,13 @@
         <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="J97" s="2">
-        <v>46337.25</v>
+        <v>46338.25</v>
       </c>
       <c r="K97" s="2">
-        <v>46337.75</v>
+        <v>46338.75</v>
       </c>
       <c r="L97" t="s">
         <v>19</v>
@@ -4363,63 +4387,63 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
         <v>204</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="F98" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K98" s="2">
-        <v>46339.333333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L98" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C99" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D99" t="s">
-        <v>61</v>
+        <v>205</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K99" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L99" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4427,307 +4451,217 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>207</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="I100" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46337.625</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46338.125</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F101" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K101" s="2">
-        <v>46339.472916666666</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L101" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D102" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K102" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D103" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D104" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F104" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K104" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D105" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>212</v>
+        <v>85</v>
       </c>
       <c r="F105" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K105" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L105" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C106" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D106" t="s">
-        <v>213</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="F106" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K106" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L106" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
-      <c r="A107" t="s">
-        <v>31</v>
-      </c>
-      <c r="B107" t="s">
-        <v>32</v>
-      </c>
-      <c r="C107" t="s">
-        <v>81</v>
-      </c>
-      <c r="D107" t="s">
-        <v>213</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F107" t="s">
-        <v>84</v>
-      </c>
-      <c r="I107" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="2">
-        <v>46339.291666666664</v>
-      </c>
-      <c r="K107" s="2">
-        <v>46340.666666666664</v>
-      </c>
-      <c r="L107" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12">
-      <c r="A108" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" t="s">
-        <v>64</v>
-      </c>
-      <c r="C108" t="s">
-        <v>90</v>
-      </c>
-      <c r="D108" t="s">
-        <v>91</v>
-      </c>
-      <c r="F108" t="s">
-        <v>67</v>
-      </c>
-      <c r="I108" t="s">
-        <v>18</v>
-      </c>
-      <c r="J108" s="2">
-        <v>46339.541666666664</v>
-      </c>
-      <c r="K108" s="2">
-        <v>46340.041666666664</v>
-      </c>
-      <c r="L108" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12">
-      <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" t="s">
-        <v>59</v>
-      </c>
-      <c r="C109" t="s">
-        <v>60</v>
-      </c>
-      <c r="D109" t="s">
-        <v>92</v>
-      </c>
-      <c r="F109" t="s">
-        <v>63</v>
-      </c>
-      <c r="I109" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K109" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L109" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -4739,15 +4673,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4755,13 +4680,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4899,18 +4824,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-20.xlsx
+++ b/data/vessels/2026-10-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442361" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FA09E69-3F4E-4AB7-86DE-1DF7D0D9CCC6}"/>
+  <xr:revisionPtr revIDLastSave="442701" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72FF0C9-E052-491E-BFD1-A4879BA017E4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -119,27 +119,30 @@
     <t>BEN LINES</t>
   </si>
   <si>
+    <t>At berth</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -173,9 +176,6 @@
     <t>MSC</t>
   </si>
   <si>
-    <t>Waiting 0.3 days</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -203,6 +203,63 @@
     <t>Matson</t>
   </si>
   <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
     <t>EB1</t>
   </si>
   <si>
@@ -218,90 +275,33 @@
     <t>Ports America Group/Pct</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
   </si>
   <si>
     <t>KW664</t>
   </si>
   <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
     <t>EB Service 1</t>
   </si>
   <si>
@@ -383,24 +383,24 @@
     <t>PN12640E</t>
   </si>
   <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
     <t>Blair</t>
   </si>
   <si>
     <t>LIBERTY PASSION</t>
   </si>
   <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
     <t>FRANKFURT EXPRESS</t>
   </si>
   <si>
@@ -431,21 +431,21 @@
     <t>1473-010E</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>PN32639E</t>
   </si>
   <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -554,16 +554,16 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>GLOVIS LEGEND</t>
@@ -1244,7 +1244,7 @@
         <v>46316.166666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1252,22 +1252,22 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1279,7 +1279,7 @@
         <v>46317.75</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1287,19 +1287,19 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1314,7 +1314,7 @@
         <v>46317.166666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1349,7 +1349,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1384,7 +1384,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1422,7 +1422,7 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1438,20 +1438,17 @@
       <c r="D10" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="1">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
         <v>56</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" t="s">
-        <v>59</v>
       </c>
       <c r="J10" s="2">
         <v>46316.25</v>
@@ -1468,34 +1465,37 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="1">
+        <v>26169</v>
+      </c>
+      <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="1">
-        <v>63</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>38</v>
+      <c r="H11" t="s">
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J11" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1503,37 +1503,31 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="1">
-        <v>26169</v>
-      </c>
       <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
         <v>65</v>
       </c>
-      <c r="G12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" t="s">
-        <v>66</v>
-      </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1541,34 +1535,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
-      <c r="H13" t="s">
-        <v>58</v>
-      </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K13" s="2">
-        <v>46317.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
@@ -1579,31 +1570,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K14" s="2">
-        <v>46318.708333333336</v>
+        <v>46321.75</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1611,31 +1605,31 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46317.875</v>
+        <v>46318.125</v>
       </c>
       <c r="K15" s="2">
-        <v>46321.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
@@ -1643,37 +1637,40 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2">
-        <v>46317.875</v>
+        <v>46318.25</v>
       </c>
       <c r="K16" s="2">
-        <v>46321.75</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1681,7 +1678,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1689,23 +1686,26 @@
       <c r="D17" t="s">
         <v>74</v>
       </c>
+      <c r="E17" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J17" s="2">
-        <v>46318.125</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K17" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.791666666664</v>
       </c>
       <c r="L17" t="s">
         <v>19</v>
@@ -1713,25 +1713,25 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
@@ -1740,13 +1740,13 @@
         <v>18</v>
       </c>
       <c r="J18" s="2">
-        <v>46318.25</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K18" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1754,37 +1754,34 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.416666666664</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K19" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1792,34 +1789,37 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="E20" s="1">
+        <v>26168</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>61</v>
+      </c>
+      <c r="H20" t="s">
+        <v>61</v>
       </c>
       <c r="I20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K20" s="2">
         <v>46319.041666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1827,37 +1827,31 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="1">
-        <v>26168</v>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="J21" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1865,31 +1859,37 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>76</v>
+      </c>
+      <c r="G22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J22" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.833333333336</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.791666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1927,7 +1927,7 @@
         <v>46320.083333333336</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1935,7 +1935,7 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -1953,7 +1953,7 @@
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J24" s="2">
         <v>46319.208333333336</v>
@@ -1982,7 +1982,7 @@
         <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
@@ -1997,7 +1997,7 @@
         <v>46325.75</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2005,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -2017,13 +2017,13 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J26" s="2">
         <v>46319.25</v>
@@ -2040,7 +2040,7 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
         <v>98</v>
@@ -2052,10 +2052,10 @@
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
@@ -2067,7 +2067,7 @@
         <v>46321.75</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2099,7 +2099,7 @@
         <v>46322</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2134,7 +2134,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2169,7 +2169,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2177,10 +2177,10 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -2189,10 +2189,10 @@
         <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
@@ -2204,7 +2204,7 @@
         <v>46323.166666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2212,31 +2212,34 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F32" t="s">
         <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s">
         <v>117</v>
       </c>
       <c r="I32" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J32" s="2">
         <v>46322.25</v>
       </c>
       <c r="K32" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L32" t="s">
         <v>19</v>
@@ -2247,34 +2250,31 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="1" t="s">
         <v>119</v>
       </c>
       <c r="F33" t="s">
         <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s">
         <v>117</v>
       </c>
       <c r="I33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J33" s="2">
         <v>46322.25</v>
       </c>
       <c r="K33" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L33" t="s">
         <v>19</v>
@@ -2312,7 +2312,7 @@
         <v>46325.75</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2347,7 +2347,7 @@
         <v>46323.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2382,7 +2382,7 @@
         <v>46323.916666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2390,7 +2390,7 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
@@ -2408,7 +2408,7 @@
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J37" s="2">
         <v>46323.25</v>
@@ -2425,10 +2425,10 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
         <v>126</v>
@@ -2437,7 +2437,7 @@
         <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
@@ -2455,7 +2455,7 @@
         <v>46325.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2463,28 +2463,28 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E39" s="1">
         <v>26173</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H39" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I39" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J39" s="2">
         <v>46323.625</v>
@@ -2493,7 +2493,7 @@
         <v>46324.041666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2501,7 +2501,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -2519,7 +2519,7 @@
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J40" s="2">
         <v>46323.791666666664</v>
@@ -2557,31 +2557,34 @@
         <v>46326</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G42" t="s">
         <v>17</v>
       </c>
+      <c r="H42" t="s">
+        <v>32</v>
+      </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
@@ -2589,21 +2592,21 @@
         <v>46324.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
         <v>133</v>
@@ -2612,14 +2615,11 @@
         <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
         <v>17</v>
       </c>
-      <c r="H43" t="s">
-        <v>32</v>
-      </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
@@ -2627,10 +2627,10 @@
         <v>46324.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2659,7 +2659,7 @@
         <v>46325.833333333336</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2667,28 +2667,28 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
         <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>85</v>
       </c>
       <c r="E45" s="1">
         <v>26172</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H45" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J45" s="2">
         <v>46325.625</v>
@@ -2697,7 +2697,7 @@
         <v>46326.041666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2732,7 +2732,7 @@
         <v>46327.416666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2740,7 +2740,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -2752,13 +2752,13 @@
         <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J47" s="2">
         <v>46326.25</v>
@@ -2775,7 +2775,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -2793,7 +2793,7 @@
         <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J48" s="2">
         <v>46326.25</v>
@@ -2813,7 +2813,7 @@
         <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s">
         <v>142</v>
@@ -2831,7 +2831,7 @@
         <v>46326.75</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2866,7 +2866,7 @@
         <v>46328.75</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2874,7 +2874,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -2886,13 +2886,13 @@
         <v>139</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J51" s="2">
         <v>46326.791666666664</v>
@@ -2909,7 +2909,7 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
         <v>98</v>
@@ -2933,7 +2933,7 @@
         <v>46329.583333333336</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2941,7 +2941,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -2959,7 +2959,7 @@
         <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J53" s="2">
         <v>46327.25</v>
@@ -2976,10 +2976,10 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
         <v>150</v>
@@ -2988,7 +2988,7 @@
         <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
@@ -3003,7 +3003,7 @@
         <v>46329.166666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3038,7 +3038,7 @@
         <v>46331.75</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3046,7 +3046,7 @@
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s">
         <v>153</v>
@@ -3058,7 +3058,7 @@
         <v>155</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G56" t="s">
         <v>17</v>
@@ -3073,7 +3073,7 @@
         <v>46328.75</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3099,7 +3099,7 @@
         <v>46328.833333333336</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3107,10 +3107,10 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D58" t="s">
         <v>157</v>
@@ -3131,7 +3131,7 @@
         <v>46331.196527777778</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3163,7 +3163,7 @@
         <v>46330</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3195,7 +3195,7 @@
         <v>46332.625</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3203,7 +3203,7 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
         <v>153</v>
@@ -3215,7 +3215,7 @@
         <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s">
         <v>17</v>
@@ -3230,7 +3230,7 @@
         <v>46330.75</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3262,7 +3262,7 @@
         <v>46334</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3294,7 +3294,7 @@
         <v>46334</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3302,19 +3302,19 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" t="s">
+        <v>60</v>
+      </c>
+      <c r="I64" t="s">
         <v>62</v>
-      </c>
-      <c r="C64" t="s">
-        <v>63</v>
-      </c>
-      <c r="D64" t="s">
-        <v>64</v>
-      </c>
-      <c r="F64" t="s">
-        <v>65</v>
-      </c>
-      <c r="I64" t="s">
-        <v>67</v>
       </c>
       <c r="J64" s="2">
         <v>46330.625</v>
@@ -3323,7 +3323,7 @@
         <v>46331.125</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3355,7 +3355,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3387,7 +3387,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3401,7 +3401,7 @@
         <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
         <v>53</v>
@@ -3416,7 +3416,7 @@
         <v>46331.204861111109</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3424,10 +3424,10 @@
         <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D68" t="s">
         <v>169</v>
@@ -3436,7 +3436,7 @@
         <v>170</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
@@ -3448,7 +3448,7 @@
         <v>46332.75</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3456,7 +3456,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -3464,17 +3464,20 @@
       <c r="D69" t="s">
         <v>171</v>
       </c>
-      <c r="E69" s="1">
-        <v>10</v>
+      <c r="E69" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F69" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s">
         <v>17</v>
       </c>
+      <c r="H69" t="s">
+        <v>173</v>
+      </c>
       <c r="I69" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J69" s="2">
         <v>46331.25</v>
@@ -3491,28 +3494,25 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="E70" s="1">
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s">
         <v>17</v>
       </c>
-      <c r="H70" t="s">
-        <v>174</v>
-      </c>
       <c r="I70" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J70" s="2">
         <v>46331.25</v>
@@ -3529,7 +3529,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -3547,7 +3547,7 @@
         <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J71" s="2">
         <v>46331.25</v>
@@ -3564,7 +3564,7 @@
         <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
         <v>153</v>
@@ -3576,7 +3576,7 @@
         <v>177</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
@@ -3588,7 +3588,7 @@
         <v>46332.166666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3596,10 +3596,10 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D73" t="s">
         <v>178</v>
@@ -3620,7 +3620,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3628,10 +3628,10 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D74" t="s">
         <v>178</v>
@@ -3652,7 +3652,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3660,28 +3660,25 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="E75" s="1">
+        <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
       </c>
-      <c r="H75" t="s">
-        <v>174</v>
-      </c>
       <c r="I75" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J75" s="2">
         <v>46331.791666666664</v>
@@ -3698,7 +3695,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -3706,17 +3703,20 @@
       <c r="D76" t="s">
         <v>171</v>
       </c>
-      <c r="E76" s="1">
-        <v>10</v>
+      <c r="E76" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F76" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s">
         <v>17</v>
       </c>
+      <c r="H76" t="s">
+        <v>173</v>
+      </c>
       <c r="I76" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J76" s="2">
         <v>46331.791666666664</v>
@@ -3733,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -3751,7 +3751,7 @@
         <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J77" s="2">
         <v>46331.791666666664</v>
@@ -3792,7 +3792,7 @@
         <v>46332.597916666666</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3821,7 +3821,7 @@
         <v>46332.791666666664</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3847,7 +3847,7 @@
         <v>46333.5</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3873,7 +3873,7 @@
         <v>46333.5</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3881,16 +3881,16 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C82" t="s">
+        <v>83</v>
+      </c>
+      <c r="D82" t="s">
         <v>84</v>
       </c>
-      <c r="D82" t="s">
-        <v>85</v>
-      </c>
       <c r="F82" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I82" t="s">
         <v>18</v>
@@ -3902,7 +3902,7 @@
         <v>46333.041666666664</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3913,7 +3913,7 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -3922,7 +3922,7 @@
         <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
@@ -3934,7 +3934,7 @@
         <v>46334.25</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3966,7 +3966,7 @@
         <v>46334</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3995,7 +3995,7 @@
         <v>46335.041666666664</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4006,10 +4006,10 @@
         <v>49</v>
       </c>
       <c r="C86" t="s">
+        <v>78</v>
+      </c>
+      <c r="D86" t="s">
         <v>79</v>
-      </c>
-      <c r="D86" t="s">
-        <v>80</v>
       </c>
       <c r="F86" t="s">
         <v>53</v>
@@ -4024,7 +4024,7 @@
         <v>46333.75</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4056,7 +4056,7 @@
         <v>46335.041666666664</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4064,7 +4064,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -4082,7 +4082,7 @@
         <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J88" s="2">
         <v>46334.25</v>
@@ -4099,7 +4099,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -4117,7 +4117,7 @@
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J89" s="2">
         <v>46334.25</v>
@@ -4134,7 +4134,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -4152,7 +4152,7 @@
         <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J90" s="2">
         <v>46334.791666666664</v>
@@ -4169,7 +4169,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
         <v>98</v>
@@ -4193,7 +4193,7 @@
         <v>46337.708333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4225,7 +4225,7 @@
         <v>46339</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4257,7 +4257,7 @@
         <v>46340.208333333336</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4286,7 +4286,7 @@
         <v>46337.833333333336</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4294,10 +4294,10 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D95" t="s">
         <v>200</v>
@@ -4306,7 +4306,7 @@
         <v>201</v>
       </c>
       <c r="F95" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
@@ -4318,7 +4318,7 @@
         <v>46339.333333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4326,19 +4326,19 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
+        <v>57</v>
+      </c>
+      <c r="C96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D96" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96" t="s">
+        <v>60</v>
+      </c>
+      <c r="I96" t="s">
         <v>62</v>
-      </c>
-      <c r="C96" t="s">
-        <v>63</v>
-      </c>
-      <c r="D96" t="s">
-        <v>64</v>
-      </c>
-      <c r="F96" t="s">
-        <v>65</v>
-      </c>
-      <c r="I96" t="s">
-        <v>67</v>
       </c>
       <c r="J96" s="2">
         <v>46337.625</v>
@@ -4347,7 +4347,7 @@
         <v>46338.125</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4355,7 +4355,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -4373,7 +4373,7 @@
         <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J97" s="2">
         <v>46338.25</v>
@@ -4411,7 +4411,7 @@
         <v>46339.472916666666</v>
       </c>
       <c r="L98" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4419,7 +4419,7 @@
         <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C99" t="s">
         <v>153</v>
@@ -4431,7 +4431,7 @@
         <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
@@ -4443,7 +4443,7 @@
         <v>46339.584027777775</v>
       </c>
       <c r="L99" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4451,10 +4451,10 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D100" t="s">
         <v>207</v>
@@ -4463,7 +4463,7 @@
         <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
@@ -4475,7 +4475,7 @@
         <v>46342.208333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4483,10 +4483,10 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D101" t="s">
         <v>207</v>
@@ -4495,7 +4495,7 @@
         <v>208</v>
       </c>
       <c r="F101" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
@@ -4507,7 +4507,7 @@
         <v>46342.208333333336</v>
       </c>
       <c r="L101" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4539,7 +4539,7 @@
         <v>46340.291666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4550,7 +4550,7 @@
         <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D103" t="s">
         <v>211</v>
@@ -4559,7 +4559,7 @@
         <v>212</v>
       </c>
       <c r="F103" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
@@ -4571,7 +4571,7 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4582,7 +4582,7 @@
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D104" t="s">
         <v>211</v>
@@ -4591,7 +4591,7 @@
         <v>212</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -4603,7 +4603,7 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4611,16 +4611,16 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C105" t="s">
+        <v>83</v>
+      </c>
+      <c r="D105" t="s">
         <v>84</v>
       </c>
-      <c r="D105" t="s">
-        <v>85</v>
-      </c>
       <c r="F105" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
@@ -4632,7 +4632,7 @@
         <v>46340.041666666664</v>
       </c>
       <c r="L105" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4646,7 +4646,7 @@
         <v>50</v>
       </c>
       <c r="D106" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F106" t="s">
         <v>53</v>
@@ -4661,7 +4661,7 @@
         <v>46340.204861111109</v>
       </c>
       <c r="L106" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4673,20 +4673,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4824,7 +4810,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4833,18 +4819,32 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-20.xlsx
+++ b/data/vessels/2026-10-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442701" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72FF0C9-E052-491E-BFD1-A4879BA017E4}"/>
+  <xr:revisionPtr revIDLastSave="443281" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9724D3B0-8092-419F-8B39-19F2254F90E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="220">
   <si>
     <t>Harbor</t>
   </si>
@@ -143,6 +143,21 @@
     <t>In transit</t>
   </si>
   <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -161,21 +176,6 @@
     <t>Inchcape</t>
   </si>
   <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -212,6 +212,15 @@
     <t>Car Carrier</t>
   </si>
   <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
     <t>TOTE</t>
   </si>
   <si>
@@ -260,9 +269,6 @@
     <t>OOCL</t>
   </si>
   <si>
-    <t>EB1</t>
-  </si>
-  <si>
     <t>ARC ENDEAVOR</t>
   </si>
   <si>
@@ -317,70 +323,85 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>PN32637W</t>
+  </si>
+  <si>
     <t>POLARIS MILA</t>
   </si>
   <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>PN12640E</t>
   </si>
   <si>
     <t>EVER SALUTE</t>
   </si>
   <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>PN12640E</t>
+    <t>129W</t>
+  </si>
+  <si>
+    <t>ACGI</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
   </si>
   <si>
     <t>LIBERTY PEACE</t>
@@ -389,61 +410,49 @@
     <t>086S</t>
   </si>
   <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
     <t>FRANKFURT EXPRESS</t>
   </si>
   <si>
     <t>640E/643W</t>
   </si>
   <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
     <t>SM PORTLAND</t>
   </si>
   <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
     <t>MSC IVANA</t>
   </si>
   <si>
     <t>UK642R</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
     <t>EVER MODE</t>
   </si>
   <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
+    <t>010W</t>
   </si>
   <si>
     <t>EB Service 2</t>
@@ -455,178 +464,190 @@
     <t>015E/016W</t>
   </si>
   <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640W</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>PN12641E</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>2606E/2606W</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>136W</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>642E</t>
+  </si>
+  <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
+    <t>FP22633C</t>
+  </si>
+  <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
+    <t>BUDAPEST EXPRESS</t>
+  </si>
+  <si>
+    <t>641E</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
+    <t>CORNEILLE</t>
+  </si>
+  <si>
+    <t>PN12642W</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
     <t>KW665</t>
   </si>
   <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN06/CPN07</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640W</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>PN12641E</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>495-136E</t>
-  </si>
-  <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>642E</t>
-  </si>
-  <si>
     <t>MSC FLORA</t>
   </si>
   <si>
     <t>MC644R</t>
   </si>
   <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
-    <t>FP22633C</t>
-  </si>
-  <si>
-    <t>BUDAPEST EXPRESS</t>
-  </si>
-  <si>
-    <t>641E</t>
-  </si>
-  <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK640A</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
+    <t>SM MUMBAI</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>DAH0C0E19</t>
+  </si>
+  <si>
+    <t>COSCO SANTOS</t>
+  </si>
+  <si>
+    <t>102N</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>1474-011E</t>
+  </si>
+  <si>
+    <t>NOCC ADRIATIC</t>
+  </si>
+  <si>
+    <t>KW667</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>LOTUS A</t>
+  </si>
+  <si>
+    <t>CPN080S19</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
+    <t>ONE MODERN</t>
+  </si>
+  <si>
+    <t>PN32641E</t>
   </si>
   <si>
     <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC638A</t>
-  </si>
-  <si>
-    <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>PN12642W</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>SM MUMBAI</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>DAH0C0E19</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>102N</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>1474-011E</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>CPN080S19</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>ONE MODERN</t>
-  </si>
-  <si>
-    <t>PN32641E</t>
   </si>
   <si>
     <t>EVER STRONG</t>
@@ -750,10 +771,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L106" totalsRowShown="0">
-  <autoFilter ref="A1:L106" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L106">
-    <sortCondition ref="J2:J106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L109" totalsRowShown="0">
+  <autoFilter ref="A1:L109" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L109">
+    <sortCondition ref="J2:J109"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1090,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1206,7 +1227,7 @@
         <v>46315.208333333336</v>
       </c>
       <c r="K3" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -1249,7 +1270,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -1267,7 +1288,7 @@
         <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1276,7 +1297,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L5" t="s">
         <v>33</v>
@@ -1284,25 +1305,25 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -1311,7 +1332,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K6" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L6" t="s">
         <v>33</v>
@@ -1445,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
         <v>56</v>
@@ -1468,34 +1489,31 @@
         <v>57</v>
       </c>
       <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
         <v>58</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="1">
-        <v>26169</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
       <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J11" s="2">
-        <v>46316.625</v>
+        <v>46316.520833333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46317.041666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1503,28 +1521,34 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
       </c>
       <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="1">
+        <v>26169</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" t="s">
         <v>65</v>
       </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
       <c r="J12" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46318.708333333336</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L12" t="s">
         <v>33</v>
@@ -1535,34 +1559,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
+      <c r="E13" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46317.875</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46321.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1576,13 +1597,13 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -1605,31 +1626,31 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J15" s="2">
-        <v>46318.125</v>
+        <v>46317.875</v>
       </c>
       <c r="K15" s="2">
-        <v>46318.916666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
@@ -1637,25 +1658,22 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
@@ -1664,51 +1682,51 @@
         <v>18</v>
       </c>
       <c r="J16" s="2">
-        <v>46318.25</v>
+        <v>46318.125</v>
       </c>
       <c r="K16" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
         <v>73</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" t="s">
         <v>75</v>
       </c>
-      <c r="F17" t="s">
-        <v>76</v>
-      </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46318.791666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1716,37 +1734,37 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
         <v>78</v>
       </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J18" s="2">
-        <v>46318.416666666664</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K18" s="2">
-        <v>46319.125</v>
+        <v>46318.791666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1754,10 +1772,10 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>81</v>
@@ -1766,22 +1784,25 @@
         <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1792,34 +1813,31 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
         <v>83</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="1">
-        <v>26168</v>
-      </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.625</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K20" s="2">
         <v>46319.041666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1827,28 +1845,34 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
+      </c>
+      <c r="E21" s="1">
+        <v>26168</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>63</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J21" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L21" t="s">
         <v>33</v>
@@ -1859,110 +1883,107 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46318.833333333336</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.791666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J23" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.833333333336</v>
       </c>
       <c r="K23" s="2">
-        <v>46320.083333333336</v>
+        <v>46319.791666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="1">
-        <v>4</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>93</v>
       </c>
-      <c r="G24" t="s">
-        <v>17</v>
+      <c r="H24" t="s">
+        <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46319.208333333336</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46319.75</v>
+        <v>46320.083333333336</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1982,7 +2003,7 @@
         <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
@@ -2005,7 +2026,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -2017,7 +2038,7 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
@@ -2040,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>98</v>
@@ -2052,10 +2073,10 @@
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
@@ -2075,31 +2096,34 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>102</v>
+      <c r="E28" s="1">
+        <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="G28" t="s">
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J28" s="2">
-        <v>46320</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="K28" s="2">
-        <v>46322</v>
+        <v>46320.75</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2110,16 +2134,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
         <v>103</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" t="s">
         <v>105</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
       </c>
       <c r="G29" t="s">
         <v>17</v>
@@ -2128,10 +2152,10 @@
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46320.25</v>
+        <v>46320.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46322.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L29" t="s">
         <v>33</v>
@@ -2145,19 +2169,19 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" t="s">
         <v>107</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" t="s">
         <v>109</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>110</v>
-      </c>
-      <c r="G30" t="s">
-        <v>111</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
@@ -2177,22 +2201,22 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
@@ -2212,37 +2236,37 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" t="s">
         <v>115</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>116</v>
       </c>
-      <c r="G32" t="s">
-        <v>39</v>
-      </c>
-      <c r="H32" t="s">
-        <v>117</v>
-      </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46322.25</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K32" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2250,22 +2274,22 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" t="s">
         <v>119</v>
       </c>
-      <c r="F33" t="s">
-        <v>116</v>
-      </c>
       <c r="G33" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I33" t="s">
         <v>56</v>
@@ -2285,58 +2309,61 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" t="s">
-        <v>17</v>
-      </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J34" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
-      <c r="H35" t="s">
-        <v>32</v>
-      </c>
       <c r="I35" t="s">
         <v>18</v>
       </c>
@@ -2344,7 +2371,7 @@
         <v>46322.625</v>
       </c>
       <c r="K35" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L35" t="s">
         <v>33</v>
@@ -2361,7 +2388,7 @@
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
         <v>53</v>
@@ -2390,16 +2417,16 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
@@ -2425,19 +2452,16 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
@@ -2449,10 +2473,10 @@
         <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46325.166666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L38" t="s">
         <v>33</v>
@@ -2463,28 +2487,28 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E39" s="1">
         <v>26173</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I39" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J39" s="2">
         <v>46323.625</v>
@@ -2498,37 +2522,40 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
         <v>17</v>
       </c>
+      <c r="H40" t="s">
+        <v>32</v>
+      </c>
       <c r="I40" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.708333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46324.75</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2536,28 +2563,34 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>117</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="G41" t="s">
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J41" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K41" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2568,16 +2601,16 @@
         <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G42" t="s">
         <v>17</v>
@@ -2603,16 +2636,16 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
         <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -2667,28 +2700,28 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E45" s="1">
         <v>26172</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H45" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I45" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J45" s="2">
         <v>46325.625</v>
@@ -2702,13 +2735,10 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
         <v>136</v>
@@ -2717,19 +2747,19 @@
         <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46325.958333333336</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K46" s="2">
-        <v>46327.416666666664</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L46" t="s">
         <v>33</v>
@@ -2740,69 +2770,66 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I47" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46326.25</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46326.75</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L47" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46326.25</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46326.75</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2810,60 +2837,60 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>16</v>
+      </c>
+      <c r="G49" t="s">
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J49" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K49" s="2">
         <v>46326.75</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
         <v>143</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F50" t="s">
-        <v>106</v>
-      </c>
-      <c r="G50" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46326.625</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46328.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L50" t="s">
         <v>33</v>
@@ -2871,37 +2898,37 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46327.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L51" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2909,19 +2936,19 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
         <v>98</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
@@ -2941,16 +2968,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -2976,19 +3003,19 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F54" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
@@ -3017,7 +3044,7 @@
         <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
@@ -3046,19 +3073,19 @@
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G56" t="s">
         <v>17</v>
@@ -3078,25 +3105,31 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>40</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K57" s="2">
-        <v>46328.833333333336</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L57" t="s">
         <v>33</v>
@@ -3104,31 +3137,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" t="s">
+        <v>32</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46327.904861111114</v>
+        <v>46328.25</v>
       </c>
       <c r="K58" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.75</v>
       </c>
       <c r="L58" t="s">
         <v>33</v>
@@ -3145,22 +3181,28 @@
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F59" t="s">
         <v>24</v>
       </c>
+      <c r="G59" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" t="s">
+        <v>116</v>
+      </c>
       <c r="I59" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46329</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K59" s="2">
-        <v>46330</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L59" t="s">
         <v>33</v>
@@ -3177,13 +3219,13 @@
         <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I60" t="s">
         <v>18</v>
@@ -3200,34 +3242,31 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>44</v>
-      </c>
-      <c r="G61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46329.708333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K61" s="2">
-        <v>46330.75</v>
+        <v>46334</v>
       </c>
       <c r="L61" t="s">
         <v>33</v>
@@ -3267,31 +3306,34 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D63" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="G63" t="s">
+        <v>17</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.291666666664</v>
       </c>
       <c r="K63" s="2">
-        <v>46334</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L63" t="s">
         <v>33</v>
@@ -3302,19 +3344,19 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J64" s="2">
         <v>46330.625</v>
@@ -3337,13 +3379,13 @@
         <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
@@ -3369,13 +3411,13 @@
         <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
@@ -3401,7 +3443,7 @@
         <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F67" t="s">
         <v>53</v>
@@ -3421,34 +3463,37 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C68" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>169</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="E68" s="1">
+        <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>44</v>
+        <v>59</v>
+      </c>
+      <c r="G68" t="s">
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J68" s="2">
-        <v>46330.75</v>
+        <v>46331.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46332.75</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3456,25 +3501,25 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s">
         <v>17</v>
       </c>
       <c r="H69" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I69" t="s">
         <v>56</v>
@@ -3491,37 +3536,37 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
-        <v>174</v>
-      </c>
-      <c r="E70" s="1">
-        <v>10</v>
+        <v>175</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="F70" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G70" t="s">
         <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L70" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3529,63 +3574,60 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D71" t="s">
-        <v>175</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F71" t="s">
-        <v>93</v>
-      </c>
-      <c r="G71" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="I71" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K71" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L71" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" t="s">
         <v>40</v>
       </c>
-      <c r="C72" t="s">
-        <v>153</v>
-      </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F72" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K72" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L72" t="s">
         <v>33</v>
@@ -3596,31 +3638,34 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
+      </c>
+      <c r="E73" s="1">
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>147</v>
+        <v>59</v>
+      </c>
+      <c r="G73" t="s">
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J73" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L73" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3628,66 +3673,69 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F74" t="s">
-        <v>147</v>
+        <v>78</v>
+      </c>
+      <c r="G74" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" t="s">
+        <v>174</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J74" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L74" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
-        <v>174</v>
-      </c>
-      <c r="E75" s="1">
-        <v>10</v>
+        <v>179</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F75" t="s">
-        <v>93</v>
-      </c>
-      <c r="G75" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="I75" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K75" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3695,31 +3743,28 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F76" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G76" t="s">
         <v>17</v>
       </c>
-      <c r="H76" t="s">
-        <v>173</v>
-      </c>
       <c r="I76" t="s">
         <v>56</v>
       </c>
       <c r="J76" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.25</v>
       </c>
       <c r="K76" s="2">
         <v>46332.75</v>
@@ -3730,66 +3775,63 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
+        <v>183</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="F77" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="G77" t="s">
         <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46332.75</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L78" t="s">
         <v>33</v>
@@ -3797,28 +3839,25 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K79" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L79" t="s">
         <v>33</v>
@@ -3832,7 +3871,7 @@
         <v>28</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F80" t="s">
         <v>31</v>
@@ -3852,25 +3891,28 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="C81" t="s">
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="F81" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46332.375</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46333.5</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L81" t="s">
         <v>33</v>
@@ -3881,28 +3923,34 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>84</v>
+        <v>181</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="F82" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="G82" t="s">
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J82" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L82" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3913,16 +3961,16 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D83" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F83" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
@@ -3945,16 +3993,16 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
@@ -3977,10 +4025,10 @@
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
@@ -4003,57 +4051,60 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C86" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>192</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F86" t="s">
-        <v>53</v>
+        <v>194</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J86" s="2">
-        <v>46333.416666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K86" s="2">
         <v>46333.75</v>
       </c>
       <c r="L86" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>189</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="F87" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="I87" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46333.666666666664</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46335.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L87" t="s">
         <v>33</v>
@@ -4061,37 +4112,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
-        <v>191</v>
-      </c>
-      <c r="E88" s="1">
-        <v>11</v>
+        <v>195</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F88" t="s">
-        <v>93</v>
-      </c>
-      <c r="G88" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="I88" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46334.25</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K88" s="2">
-        <v>46334.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L88" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4099,16 +4147,16 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
@@ -4134,19 +4182,19 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>192</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
+      </c>
+      <c r="E90" s="1">
+        <v>11</v>
       </c>
       <c r="F90" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G90" t="s">
         <v>17</v>
@@ -4155,10 +4203,10 @@
         <v>56</v>
       </c>
       <c r="J90" s="2">
-        <v>46334.791666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46335.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L90" t="s">
         <v>19</v>
@@ -4169,31 +4217,34 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
       </c>
+      <c r="G91" t="s">
+        <v>17</v>
+      </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J91" s="2">
-        <v>46334.958333333336</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K91" s="2">
-        <v>46337.708333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L91" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4201,28 +4252,28 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="D92" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46337</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K92" s="2">
-        <v>46339</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L92" t="s">
         <v>33</v>
@@ -4233,31 +4284,34 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>198</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="G93" t="s">
+        <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J93" s="2">
-        <v>46337.208333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K93" s="2">
-        <v>46340.208333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L93" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4265,57 +4319,63 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>202</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>53</v>
+        <v>59</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J94" s="2">
-        <v>46337.333333333336</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46337.833333333336</v>
+        <v>46336.75</v>
       </c>
       <c r="L94" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46337.333333333336</v>
+        <v>46337</v>
       </c>
       <c r="K95" s="2">
-        <v>46339.333333333336</v>
+        <v>46339</v>
       </c>
       <c r="L95" t="s">
         <v>33</v>
@@ -4326,25 +4386,28 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>59</v>
+        <v>205</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F96" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="I96" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46337.625</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46338.125</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L96" t="s">
         <v>33</v>
@@ -4355,34 +4418,28 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>202</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
-      </c>
-      <c r="G97" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I97" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46338.25</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46338.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4390,25 +4447,28 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F98" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46338.431250000001</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L98" t="s">
         <v>33</v>
@@ -4416,31 +4476,28 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C99" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D99" t="s">
-        <v>205</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="F99" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J99" s="2">
-        <v>46338.709027777775</v>
+        <v>46337.625</v>
       </c>
       <c r="K99" s="2">
-        <v>46339.584027777775</v>
+        <v>46338.125</v>
       </c>
       <c r="L99" t="s">
         <v>33</v>
@@ -4451,60 +4508,60 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="C100" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F100" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="G100" t="s">
+        <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="J100" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.25</v>
       </c>
       <c r="K100" s="2">
-        <v>46342.208333333336</v>
+        <v>46338.75</v>
       </c>
       <c r="L100" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="D101" t="s">
-        <v>207</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K101" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L101" t="s">
         <v>33</v>
@@ -4515,28 +4572,28 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="D102" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F102" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46339.083333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K102" s="2">
-        <v>46340.291666666664</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L102" t="s">
         <v>33</v>
@@ -4544,31 +4601,31 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D103" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F103" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46339.291666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K103" s="2">
-        <v>46340.666666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L103" t="s">
         <v>33</v>
@@ -4576,31 +4633,31 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C104" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D104" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46339.291666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K104" s="2">
-        <v>46340.666666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L104" t="s">
         <v>33</v>
@@ -4608,28 +4665,31 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D105" t="s">
-        <v>84</v>
+        <v>216</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="F105" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46339.541666666664</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K105" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L105" t="s">
         <v>33</v>
@@ -4637,30 +4697,123 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B106" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106" t="s">
+        <v>72</v>
+      </c>
+      <c r="D106" t="s">
+        <v>218</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F106" t="s">
+        <v>75</v>
+      </c>
+      <c r="I106" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="2">
+        <v>46339.291666666664</v>
+      </c>
+      <c r="K106" s="2">
+        <v>46340.666666666664</v>
+      </c>
+      <c r="L106" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" t="s">
+        <v>72</v>
+      </c>
+      <c r="D107" t="s">
+        <v>218</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="2">
+        <v>46339.291666666664</v>
+      </c>
+      <c r="K107" s="2">
+        <v>46340.666666666664</v>
+      </c>
+      <c r="L107" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" t="s">
+        <v>60</v>
+      </c>
+      <c r="C108" t="s">
+        <v>85</v>
+      </c>
+      <c r="D108" t="s">
+        <v>86</v>
+      </c>
+      <c r="F108" t="s">
+        <v>63</v>
+      </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="2">
+        <v>46339.541666666664</v>
+      </c>
+      <c r="K108" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L108" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
         <v>49</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C109" t="s">
         <v>50</v>
       </c>
-      <c r="D106" t="s">
-        <v>85</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="D109" t="s">
+        <v>87</v>
+      </c>
+      <c r="F109" t="s">
         <v>53</v>
       </c>
-      <c r="I106" t="s">
-        <v>18</v>
-      </c>
-      <c r="J106" s="2">
+      <c r="I109" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="2">
         <v>46339.704861111109</v>
       </c>
-      <c r="K106" s="2">
+      <c r="K109" s="2">
         <v>46340.204861111109</v>
       </c>
-      <c r="L106" t="s">
+      <c r="L109" t="s">
         <v>33</v>
       </c>
     </row>
